--- a/diseases/d040/1995-1999.xlsx
+++ b/diseases/d040/1995-1999.xlsx
@@ -21143,6 +21143,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO104" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22163,6 +22168,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO109" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22944,6 +22954,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO113" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23725,6 +23740,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO117" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24506,6 +24526,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO121" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25287,6 +25312,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO125" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26068,6 +26098,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO129" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26849,6 +26884,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO133" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27630,6 +27670,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO137" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28411,6 +28456,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO141" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29192,6 +29242,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO145" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29973,6 +30028,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO149" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31144,6 +31204,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO155" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32564,6 +32629,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO162" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33745,6 +33815,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO168" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34926,6 +35001,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO174" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36107,6 +36187,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO180" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37288,6 +37373,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO186" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38469,6 +38559,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO192" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39650,6 +39745,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO198" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40831,6 +40931,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO204" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42012,6 +42117,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA210" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO210" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43193,6 +43303,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA216" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO216" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44374,6 +44489,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA222" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO222" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45945,6 +46065,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA230" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO230" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -47365,6 +47490,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA237" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO237" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48546,6 +48676,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA243" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO243" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49727,6 +49862,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA249" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO249" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50908,6 +51048,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA255" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO255" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52089,6 +52234,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA261" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO261" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -53270,6 +53420,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA267" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO267" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -54451,6 +54606,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA273" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO273" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -55632,6 +55792,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA279" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO279" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -56813,6 +56978,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA285" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO285" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -57994,6 +58164,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA291" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO291" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -59173,6 +59348,11 @@
       <c r="S297" t="inlineStr">
         <is>
           <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA297" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO297" t="inlineStr">

--- a/diseases/d040/1995-1999.xlsx
+++ b/diseases/d040/1995-1999.xlsx
@@ -21138,6 +21138,11 @@
       <c r="Q104" t="n">
         <v>0</v>
       </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21150,13 +21155,23 @@
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR104" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS104" t="inlineStr"/>
       <c r="AT104" t="n">
         <v>0</v>
       </c>
+      <c r="AU104" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV104" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -22148,6 +22163,11 @@
       <c r="Q109" t="n">
         <v>0</v>
       </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22160,13 +22180,23 @@
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR109" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS109" t="inlineStr"/>
       <c r="AT109" t="n">
         <v>0</v>
       </c>
+      <c r="AU109" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV109" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -22919,6 +22949,11 @@
       <c r="Q113" t="n">
         <v>0</v>
       </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22931,13 +22966,23 @@
       </c>
       <c r="AP113" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR113" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS113" t="inlineStr"/>
       <c r="AT113" t="n">
         <v>0</v>
       </c>
+      <c r="AU113" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV113" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -23690,6 +23735,11 @@
       <c r="Q117" t="n">
         <v>0</v>
       </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23702,13 +23752,23 @@
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR117" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS117" t="inlineStr"/>
       <c r="AT117" t="n">
         <v>0</v>
       </c>
+      <c r="AU117" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV117" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -24461,6 +24521,11 @@
       <c r="Q121" t="n">
         <v>0</v>
       </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24473,13 +24538,23 @@
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR121" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS121" t="inlineStr"/>
       <c r="AT121" t="n">
         <v>0</v>
       </c>
+      <c r="AU121" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV121" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -25232,6 +25307,11 @@
       <c r="Q125" t="n">
         <v>0</v>
       </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25244,13 +25324,23 @@
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR125" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS125" t="inlineStr"/>
       <c r="AT125" t="n">
         <v>0</v>
       </c>
+      <c r="AU125" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV125" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -26003,6 +26093,11 @@
       <c r="Q129" t="n">
         <v>0</v>
       </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -26015,13 +26110,23 @@
       </c>
       <c r="AP129" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR129" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS129" t="inlineStr"/>
       <c r="AT129" t="n">
         <v>0</v>
       </c>
+      <c r="AU129" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV129" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -26774,6 +26879,11 @@
       <c r="Q133" t="n">
         <v>0</v>
       </c>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA133" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -26786,13 +26896,23 @@
       </c>
       <c r="AP133" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR133" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS133" t="inlineStr"/>
       <c r="AT133" t="n">
         <v>0</v>
       </c>
+      <c r="AU133" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV133" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -27545,6 +27665,11 @@
       <c r="Q137" t="n">
         <v>0</v>
       </c>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA137" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -27557,13 +27682,23 @@
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR137" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS137" t="inlineStr"/>
       <c r="AT137" t="n">
         <v>0</v>
       </c>
+      <c r="AU137" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV137" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -28316,6 +28451,11 @@
       <c r="Q141" t="n">
         <v>0</v>
       </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA141" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -28328,13 +28468,23 @@
       </c>
       <c r="AP141" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR141" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS141" t="inlineStr"/>
       <c r="AT141" t="n">
         <v>0</v>
       </c>
+      <c r="AU141" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV141" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -29087,6 +29237,11 @@
       <c r="Q145" t="n">
         <v>0</v>
       </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA145" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -29099,13 +29254,23 @@
       </c>
       <c r="AP145" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR145" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS145" t="inlineStr"/>
       <c r="AT145" t="n">
         <v>0</v>
       </c>
+      <c r="AU145" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV145" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -29858,6 +30023,11 @@
       <c r="Q149" t="n">
         <v>0</v>
       </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA149" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -29870,13 +30040,23 @@
       </c>
       <c r="AP149" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR149" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS149" t="inlineStr"/>
       <c r="AT149" t="n">
         <v>0</v>
       </c>
+      <c r="AU149" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV149" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -31019,6 +31199,11 @@
       <c r="Q155" t="n">
         <v>0</v>
       </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA155" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -31031,13 +31216,23 @@
       </c>
       <c r="AP155" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR155" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS155" t="inlineStr"/>
       <c r="AT155" t="n">
         <v>0</v>
       </c>
+      <c r="AU155" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV155" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -32429,6 +32624,11 @@
       <c r="Q162" t="n">
         <v>0</v>
       </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA162" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -32441,13 +32641,23 @@
       </c>
       <c r="AP162" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR162" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS162" t="inlineStr"/>
       <c r="AT162" t="n">
         <v>0</v>
       </c>
+      <c r="AU162" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV162" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -33600,6 +33810,11 @@
       <c r="Q168" t="n">
         <v>0</v>
       </c>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA168" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -33612,13 +33827,23 @@
       </c>
       <c r="AP168" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR168" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS168" t="inlineStr"/>
       <c r="AT168" t="n">
         <v>0</v>
       </c>
+      <c r="AU168" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV168" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -34771,6 +34996,11 @@
       <c r="Q174" t="n">
         <v>0</v>
       </c>
+      <c r="S174" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA174" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -34783,13 +35013,23 @@
       </c>
       <c r="AP174" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR174" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS174" t="inlineStr"/>
       <c r="AT174" t="n">
         <v>0</v>
       </c>
+      <c r="AU174" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV174" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -35942,6 +36182,11 @@
       <c r="Q180" t="n">
         <v>0</v>
       </c>
+      <c r="S180" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA180" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -35954,13 +36199,23 @@
       </c>
       <c r="AP180" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR180" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS180" t="inlineStr"/>
       <c r="AT180" t="n">
         <v>0</v>
       </c>
+      <c r="AU180" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV180" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -37113,6 +37368,11 @@
       <c r="Q186" t="n">
         <v>0</v>
       </c>
+      <c r="S186" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA186" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -37125,13 +37385,23 @@
       </c>
       <c r="AP186" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR186" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS186" t="inlineStr"/>
       <c r="AT186" t="n">
         <v>0</v>
       </c>
+      <c r="AU186" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV186" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -38284,6 +38554,11 @@
       <c r="Q192" t="n">
         <v>0</v>
       </c>
+      <c r="S192" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA192" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -38296,13 +38571,23 @@
       </c>
       <c r="AP192" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR192" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS192" t="inlineStr"/>
       <c r="AT192" t="n">
         <v>0</v>
       </c>
+      <c r="AU192" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV192" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -39455,6 +39740,11 @@
       <c r="Q198" t="n">
         <v>0</v>
       </c>
+      <c r="S198" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA198" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -39467,13 +39757,23 @@
       </c>
       <c r="AP198" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR198" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS198" t="inlineStr"/>
       <c r="AT198" t="n">
         <v>0</v>
       </c>
+      <c r="AU198" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV198" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -40626,6 +40926,11 @@
       <c r="Q204" t="n">
         <v>0</v>
       </c>
+      <c r="S204" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA204" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -40638,13 +40943,23 @@
       </c>
       <c r="AP204" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR204" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS204" t="inlineStr"/>
       <c r="AT204" t="n">
         <v>0</v>
       </c>
+      <c r="AU204" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV204" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -41797,6 +42112,11 @@
       <c r="Q210" t="n">
         <v>0</v>
       </c>
+      <c r="S210" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA210" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -41809,13 +42129,23 @@
       </c>
       <c r="AP210" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR210" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS210" t="inlineStr"/>
       <c r="AT210" t="n">
         <v>0</v>
       </c>
+      <c r="AU210" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV210" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -42968,6 +43298,11 @@
       <c r="Q216" t="n">
         <v>0</v>
       </c>
+      <c r="S216" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA216" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -42980,13 +43315,23 @@
       </c>
       <c r="AP216" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR216" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS216" t="inlineStr"/>
       <c r="AT216" t="n">
         <v>0</v>
       </c>
+      <c r="AU216" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV216" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -44139,6 +44484,11 @@
       <c r="Q222" t="n">
         <v>0</v>
       </c>
+      <c r="S222" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA222" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -44151,13 +44501,23 @@
       </c>
       <c r="AP222" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR222" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS222" t="inlineStr"/>
       <c r="AT222" t="n">
         <v>0</v>
       </c>
+      <c r="AU222" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV222" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -45700,6 +46060,11 @@
       <c r="Q230" t="n">
         <v>0</v>
       </c>
+      <c r="S230" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA230" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -45712,13 +46077,23 @@
       </c>
       <c r="AP230" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR230" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS230" t="inlineStr"/>
       <c r="AT230" t="n">
         <v>0</v>
       </c>
+      <c r="AU230" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV230" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -47110,6 +47485,11 @@
       <c r="Q237" t="n">
         <v>0</v>
       </c>
+      <c r="S237" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA237" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -47122,13 +47502,23 @@
       </c>
       <c r="AP237" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR237" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS237" t="inlineStr"/>
       <c r="AT237" t="n">
         <v>0</v>
       </c>
+      <c r="AU237" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV237" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -48281,6 +48671,11 @@
       <c r="Q243" t="n">
         <v>0</v>
       </c>
+      <c r="S243" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA243" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -48293,13 +48688,23 @@
       </c>
       <c r="AP243" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR243" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS243" t="inlineStr"/>
       <c r="AT243" t="n">
         <v>0</v>
       </c>
+      <c r="AU243" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV243" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -49452,6 +49857,11 @@
       <c r="Q249" t="n">
         <v>0</v>
       </c>
+      <c r="S249" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA249" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -49464,13 +49874,23 @@
       </c>
       <c r="AP249" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR249" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS249" t="inlineStr"/>
       <c r="AT249" t="n">
         <v>0</v>
       </c>
+      <c r="AU249" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV249" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -50623,6 +51043,11 @@
       <c r="Q255" t="n">
         <v>0</v>
       </c>
+      <c r="S255" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA255" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -50635,13 +51060,23 @@
       </c>
       <c r="AP255" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR255" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS255" t="inlineStr"/>
       <c r="AT255" t="n">
         <v>0</v>
       </c>
+      <c r="AU255" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV255" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -51794,6 +52229,11 @@
       <c r="Q261" t="n">
         <v>0</v>
       </c>
+      <c r="S261" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA261" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -51806,13 +52246,23 @@
       </c>
       <c r="AP261" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR261" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS261" t="inlineStr"/>
       <c r="AT261" t="n">
         <v>0</v>
       </c>
+      <c r="AU261" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV261" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -52965,6 +53415,11 @@
       <c r="Q267" t="n">
         <v>0</v>
       </c>
+      <c r="S267" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA267" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -52977,13 +53432,23 @@
       </c>
       <c r="AP267" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR267" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS267" t="inlineStr"/>
       <c r="AT267" t="n">
         <v>0</v>
       </c>
+      <c r="AU267" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV267" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -54136,6 +54601,11 @@
       <c r="Q273" t="n">
         <v>0</v>
       </c>
+      <c r="S273" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA273" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -54148,13 +54618,23 @@
       </c>
       <c r="AP273" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR273" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS273" t="inlineStr"/>
       <c r="AT273" t="n">
         <v>0</v>
       </c>
+      <c r="AU273" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV273" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -55307,6 +55787,11 @@
       <c r="Q279" t="n">
         <v>0</v>
       </c>
+      <c r="S279" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA279" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -55319,13 +55804,23 @@
       </c>
       <c r="AP279" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR279" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS279" t="inlineStr"/>
       <c r="AT279" t="n">
         <v>0</v>
       </c>
+      <c r="AU279" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV279" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -56478,6 +56973,11 @@
       <c r="Q285" t="n">
         <v>0</v>
       </c>
+      <c r="S285" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA285" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -56490,13 +56990,23 @@
       </c>
       <c r="AP285" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR285" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS285" t="inlineStr"/>
       <c r="AT285" t="n">
         <v>0</v>
       </c>
+      <c r="AU285" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV285" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -57649,6 +58159,11 @@
       <c r="Q291" t="n">
         <v>0</v>
       </c>
+      <c r="S291" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA291" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -57661,13 +58176,23 @@
       </c>
       <c r="AP291" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR291" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS291" t="inlineStr"/>
       <c r="AT291" t="n">
         <v>0</v>
       </c>
+      <c r="AU291" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV291" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -58820,6 +59345,11 @@
       <c r="Q297" t="n">
         <v>0</v>
       </c>
+      <c r="S297" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA297" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -58832,12 +59362,22 @@
       </c>
       <c r="AP297" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR297" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS297" t="inlineStr"/>
       <c r="AT297" t="n">
         <v>0</v>
+      </c>
+      <c r="AU297" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV297" t="inlineStr">
         <is>
